--- a/docs/qa/TASK-040/reviewer-r2-blind-review.xlsx
+++ b/docs/qa/TASK-040/reviewer-r2-blind-review.xlsx
@@ -4,477 +4,480 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Review" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Metadata" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="评审" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="说明" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="元数据" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="367">
-  <si>
-    <t>Row</t>
-  </si>
-  <si>
-    <t>Blind Item ID</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Traveler Intent</t>
-  </si>
-  <si>
-    <t>POI A</t>
-  </si>
-  <si>
-    <t>A Prefecture</t>
-  </si>
-  <si>
-    <t>A Region</t>
-  </si>
-  <si>
-    <t>A Category</t>
-  </si>
-  <si>
-    <t>A Source 1</t>
-  </si>
-  <si>
-    <t>A Source 2</t>
-  </si>
-  <si>
-    <t>POI B</t>
-  </si>
-  <si>
-    <t>B Prefecture</t>
-  </si>
-  <si>
-    <t>B Region</t>
-  </si>
-  <si>
-    <t>B Category</t>
-  </si>
-  <si>
-    <t>B Source 1</t>
-  </si>
-  <si>
-    <t>B Source 2</t>
-  </si>
-  <si>
-    <t>Choice</t>
-  </si>
-  <si>
-    <t>Confidence</t>
-  </si>
-  <si>
-    <t>Note</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="370">
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>盲审题目 ID</t>
+  </si>
+  <si>
+    <t>旅行场景</t>
+  </si>
+  <si>
+    <t>旅客需求</t>
+  </si>
+  <si>
+    <t>景点 A</t>
+  </si>
+  <si>
+    <t>A 所在都道府县</t>
+  </si>
+  <si>
+    <t>A 所在地区</t>
+  </si>
+  <si>
+    <t>A 类型</t>
+  </si>
+  <si>
+    <t>A 来源 1</t>
+  </si>
+  <si>
+    <t>A 来源 2</t>
+  </si>
+  <si>
+    <t>景点 B</t>
+  </si>
+  <si>
+    <t>B 所在都道府县</t>
+  </si>
+  <si>
+    <t>B 所在地区</t>
+  </si>
+  <si>
+    <t>B 类型</t>
+  </si>
+  <si>
+    <t>B 来源 1</t>
+  </si>
+  <si>
+    <t>B 来源 2</t>
+  </si>
+  <si>
+    <t>选择</t>
+  </si>
+  <si>
+    <t>置信度</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>R2-08DB03F8E019</t>
   </si>
   <si>
-    <t>Hidden and local explorer</t>
-  </si>
-  <si>
-    <t>A repeat visitor prefers locally distinctive places away from the most obvious headline sights.</t>
-  </si>
-  <si>
-    <t>Hirosaki Castle</t>
-  </si>
-  <si>
-    <t>Aomori</t>
-  </si>
-  <si>
-    <t>Tohoku</t>
-  </si>
-  <si>
-    <t>Park</t>
-  </si>
-  <si>
-    <t>Source 1</t>
-  </si>
-  <si>
-    <t>Source 2</t>
-  </si>
-  <si>
-    <t>Nijō Castle</t>
-  </si>
-  <si>
-    <t>Kyoto</t>
-  </si>
-  <si>
-    <t>Kansai</t>
-  </si>
-  <si>
-    <t>Garden</t>
+    <t>在地小众探索</t>
+  </si>
+  <si>
+    <t>曾多次访问日本，希望探索具有地方特色、避开热门地标的地点。</t>
+  </si>
+  <si>
+    <t>弘前城</t>
+  </si>
+  <si>
+    <t>青森县</t>
+  </si>
+  <si>
+    <t>东北</t>
+  </si>
+  <si>
+    <t>公园</t>
+  </si>
+  <si>
+    <t>来源 1</t>
+  </si>
+  <si>
+    <t>来源 2</t>
+  </si>
+  <si>
+    <t>二条城</t>
+  </si>
+  <si>
+    <t>京都府</t>
+  </si>
+  <si>
+    <t>关西</t>
+  </si>
+  <si>
+    <t>庭园</t>
   </si>
   <si>
     <t>R2-1369CE04815A</t>
   </si>
   <si>
-    <t>First-time iconic traveler</t>
-  </si>
-  <si>
-    <t>A first-time visitor wants a memorable, widely recognizable introduction to Japan.</t>
-  </si>
-  <si>
-    <t>Okinawa Prefectural Museum</t>
-  </si>
-  <si>
-    <t>Okinawa</t>
-  </si>
-  <si>
-    <t>Museum</t>
-  </si>
-  <si>
-    <t>Osaka Aquarium Kaiyukan</t>
-  </si>
-  <si>
-    <t>Osaka</t>
-  </si>
-  <si>
-    <t>Entertainment venue</t>
+    <t>初次访日经典体验</t>
+  </si>
+  <si>
+    <t>首次前往日本，希望获得难忘且具有代表性的日本旅行体验。</t>
+  </si>
+  <si>
+    <t>冲绳县立博物馆、美术馆</t>
+  </si>
+  <si>
+    <t>冲绳县</t>
+  </si>
+  <si>
+    <t>冲绳</t>
+  </si>
+  <si>
+    <t>博物馆</t>
+  </si>
+  <si>
+    <t>海游馆</t>
+  </si>
+  <si>
+    <t>大阪府</t>
+  </si>
+  <si>
+    <t>娱乐设施</t>
   </si>
   <si>
     <t>R2-3675AD775AC8</t>
   </si>
   <si>
-    <t>Nature traveler</t>
-  </si>
-  <si>
-    <t>A traveler wants nature, landscapes, parks, or outdoor exploration.</t>
-  </si>
-  <si>
-    <t>Jigokudani Monkey Park</t>
-  </si>
-  <si>
-    <t>Nagano</t>
-  </si>
-  <si>
-    <t>Chubu</t>
-  </si>
-  <si>
-    <t>Natural place</t>
-  </si>
-  <si>
-    <t>Kyoto National Museum</t>
+    <t>自然旅行</t>
+  </si>
+  <si>
+    <t>希望探索自然、山水、公园或户外景观。</t>
+  </si>
+  <si>
+    <t>地狱谷野猿公苑</t>
+  </si>
+  <si>
+    <t>长野县</t>
+  </si>
+  <si>
+    <t>中部</t>
+  </si>
+  <si>
+    <t>自然景点</t>
+  </si>
+  <si>
+    <t>京都国立博物馆</t>
   </si>
   <si>
     <t>R2-D23DFFFF9CE9</t>
   </si>
   <si>
-    <t>History and architecture</t>
-  </si>
-  <si>
-    <t>A traveler is especially interested in history, heritage, and architecture.</t>
-  </si>
-  <si>
-    <t>Huis Ten Bosch (theme park)</t>
-  </si>
-  <si>
-    <t>Nagasaki</t>
-  </si>
-  <si>
-    <t>Kyushu</t>
-  </si>
-  <si>
-    <t>Mount Fuji</t>
-  </si>
-  <si>
-    <t>Shizuoka</t>
-  </si>
-  <si>
-    <t>Mountain or highland place</t>
+    <t>历史与建筑</t>
+  </si>
+  <si>
+    <t>对历史、文化遗产与建筑尤其感兴趣。</t>
+  </si>
+  <si>
+    <t>豪斯登堡</t>
+  </si>
+  <si>
+    <t>长崎县</t>
+  </si>
+  <si>
+    <t>九州</t>
+  </si>
+  <si>
+    <t>富士山</t>
+  </si>
+  <si>
+    <t>静冈县</t>
+  </si>
+  <si>
+    <t>山岳或高原</t>
   </si>
   <si>
     <t>R2-757753ADD229</t>
   </si>
   <si>
-    <t>Family and interactive soft fit</t>
-  </si>
-  <si>
-    <t>A family group prefers engaging, interactive places with broad age appeal.</t>
-  </si>
-  <si>
-    <t>Kiyomizu-dera</t>
-  </si>
-  <si>
-    <t>Temple or religious site</t>
-  </si>
-  <si>
-    <t>Zenkō-ji</t>
+    <t>亲子互动</t>
+  </si>
+  <si>
+    <t>家庭同行，希望选择互动性强、适合不同年龄段的地点。</t>
+  </si>
+  <si>
+    <t>清水寺</t>
+  </si>
+  <si>
+    <t>寺庙或宗教场所</t>
+  </si>
+  <si>
+    <t>善光寺</t>
   </si>
   <si>
     <t>R2-F5F4403E9CFF</t>
   </si>
   <si>
-    <t>Shopping and city traveler</t>
-  </si>
-  <si>
-    <t>A traveler prefers shopping, lively neighborhoods, and contemporary city experiences.</t>
-  </si>
-  <si>
-    <t>Mōtsū-ji</t>
-  </si>
-  <si>
-    <t>Iwate</t>
-  </si>
-  <si>
-    <t>Izumo-taisha</t>
-  </si>
-  <si>
-    <t>Shimane</t>
-  </si>
-  <si>
-    <t>Chugoku</t>
-  </si>
-  <si>
-    <t>Shrine or religious site</t>
+    <t>购物与都市体验</t>
+  </si>
+  <si>
+    <t>喜欢购物、热闹街区与现代都市体验。</t>
+  </si>
+  <si>
+    <t>毛越寺</t>
+  </si>
+  <si>
+    <t>岩手县</t>
+  </si>
+  <si>
+    <t>出云大社</t>
+  </si>
+  <si>
+    <t>岛根县</t>
+  </si>
+  <si>
+    <t>中国地区</t>
+  </si>
+  <si>
+    <t>神社或宗教场所</t>
   </si>
   <si>
     <t>R2-75D1696C1577</t>
   </si>
   <si>
-    <t>Tokyo Tower</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Kanto</t>
-  </si>
-  <si>
-    <t>Scenic viewpoint</t>
+    <t>东京铁塔</t>
+  </si>
+  <si>
+    <t>东京都</t>
+  </si>
+  <si>
+    <t>关东</t>
+  </si>
+  <si>
+    <t>景观眺望点</t>
   </si>
   <si>
     <t>R2-5162B9E62E9E</t>
   </si>
   <si>
-    <t>Relaxed and rest-oriented traveler</t>
-  </si>
-  <si>
-    <t>A traveler wants a calm, restorative day with a relaxed pace.</t>
-  </si>
-  <si>
-    <t>Sensō-ji</t>
+    <t>轻松疗愈</t>
+  </si>
+  <si>
+    <t>希望以舒缓节奏度过平静、放松的一天。</t>
+  </si>
+  <si>
+    <t>浅草寺</t>
   </si>
   <si>
     <t>R2-B2662897C7D7</t>
   </si>
   <si>
-    <t>Low crowd and queue tolerance</t>
-  </si>
-  <si>
-    <t>A traveler has low tolerance for crowds and long queues.</t>
-  </si>
-  <si>
-    <t>Ōtsuka Museum of Art</t>
-  </si>
-  <si>
-    <t>Tokushima</t>
-  </si>
-  <si>
-    <t>Shikoku</t>
+    <t>避开拥挤</t>
+  </si>
+  <si>
+    <t>对拥挤人群和长时间排队的承受能力较低。</t>
+  </si>
+  <si>
+    <t>大冢国际美术馆</t>
+  </si>
+  <si>
+    <t>德岛县</t>
+  </si>
+  <si>
+    <t>四国</t>
   </si>
   <si>
     <t>R2-93DB1C11FEC5</t>
   </si>
   <si>
-    <t>Odori Park</t>
-  </si>
-  <si>
-    <t>Hokkaido</t>
-  </si>
-  <si>
-    <t>Kōraku-en</t>
-  </si>
-  <si>
-    <t>Okayama</t>
+    <t>大通公园</t>
+  </si>
+  <si>
+    <t>北海道</t>
+  </si>
+  <si>
+    <t>后乐园</t>
+  </si>
+  <si>
+    <t>冈山县</t>
   </si>
   <si>
     <t>R2-5BEF96B330FF</t>
   </si>
   <si>
-    <t>Universal Studios Japan</t>
-  </si>
-  <si>
-    <t>Dōgo Onsen</t>
-  </si>
-  <si>
-    <t>Ehime</t>
-  </si>
-  <si>
-    <t>Historic place</t>
+    <t>日本环球影城</t>
+  </si>
+  <si>
+    <t>道后温泉</t>
+  </si>
+  <si>
+    <t>爱媛县</t>
+  </si>
+  <si>
+    <t>历史景点</t>
   </si>
   <si>
     <t>R2-71EAB7C26A89</t>
   </si>
   <si>
-    <t>Ritsurin Garden</t>
-  </si>
-  <si>
-    <t>Kagawa</t>
+    <t>栗林公园</t>
+  </si>
+  <si>
+    <t>香川县</t>
   </si>
   <si>
     <t>R2-782620FDA993</t>
   </si>
   <si>
-    <t>Food-focused traveler</t>
-  </si>
-  <si>
-    <t>A traveler wants food culture and local eating experiences to lead the day.</t>
-  </si>
-  <si>
-    <t>Shirakawa, Gifu (village)</t>
-  </si>
-  <si>
-    <t>Gifu</t>
-  </si>
-  <si>
-    <t>Sannai-Maruyama Site</t>
+    <t>美食主题</t>
+  </si>
+  <si>
+    <t>希望以饮食文化和当地美食体验为行程核心。</t>
+  </si>
+  <si>
+    <t>白川村</t>
+  </si>
+  <si>
+    <t>岐阜县</t>
+  </si>
+  <si>
+    <t>三内丸山遗址</t>
   </si>
   <si>
     <t>R2-7C5949080439</t>
   </si>
   <si>
-    <t>Okinawa Churaumi Aquarium</t>
+    <t>冲绳美丽海水族馆</t>
   </si>
   <si>
     <t>R2-E9F153EAF9A1</t>
   </si>
   <si>
-    <t>Low walking and physical tolerance</t>
-  </si>
-  <si>
-    <t>A traveler has low tolerance for prolonged walking or physical effort.</t>
-  </si>
-  <si>
-    <t>Oirase River</t>
-  </si>
-  <si>
-    <t>Moerenuma Park</t>
-  </si>
-  <si>
-    <t>Art or cultural venue</t>
+    <t>少步行需求</t>
+  </si>
+  <si>
+    <t>对长时间步行或体力消耗的承受能力较低。</t>
+  </si>
+  <si>
+    <t>奥入濑川</t>
+  </si>
+  <si>
+    <t>莫埃来沼公园</t>
+  </si>
+  <si>
+    <t>艺术或文化场馆</t>
   </si>
   <si>
     <t>R2-4DDA66516836</t>
   </si>
   <si>
-    <t>Photography and scenery</t>
-  </si>
-  <si>
-    <t>A traveler prioritizes rewarding photography opportunities and attractive scenery.</t>
-  </si>
-  <si>
-    <t>Ghibli Museum</t>
-  </si>
-  <si>
-    <t>Iya Valley</t>
+    <t>摄影与风景</t>
+  </si>
+  <si>
+    <t>重视摄影机会和优美景观。</t>
+  </si>
+  <si>
+    <t>三鹰之森吉卜力美术馆</t>
+  </si>
+  <si>
+    <t>祖谷溪</t>
   </si>
   <si>
     <t>R2-215993FBD22A</t>
   </si>
   <si>
-    <t>Osaka Castle</t>
-  </si>
-  <si>
-    <t>Rurikō-ji</t>
-  </si>
-  <si>
-    <t>Yamaguchi</t>
+    <t>大阪城</t>
+  </si>
+  <si>
+    <t>瑠璃光寺</t>
+  </si>
+  <si>
+    <t>山口县</t>
   </si>
   <si>
     <t>R2-E6FBF8365FDC</t>
   </si>
   <si>
-    <t>Zuihōden</t>
-  </si>
-  <si>
-    <t>Miyagi</t>
-  </si>
-  <si>
-    <t>Adachi Museum of Art</t>
+    <t>瑞凤殿</t>
+  </si>
+  <si>
+    <t>宫城县</t>
+  </si>
+  <si>
+    <t>足立美术馆</t>
   </si>
   <si>
     <t>R2-3EB362DAAB1D</t>
   </si>
   <si>
-    <t>Tokyo Skytree</t>
-  </si>
-  <si>
-    <t>Kōchi Castle</t>
-  </si>
-  <si>
-    <t>Kochi</t>
+    <t>东京晴空塔</t>
+  </si>
+  <si>
+    <t>高知城</t>
+  </si>
+  <si>
+    <t>高知县</t>
   </si>
   <si>
     <t>R2-9A4B37F1D8A9</t>
   </si>
   <si>
-    <t>Atsuta Shrine</t>
-  </si>
-  <si>
-    <t>Aichi</t>
+    <t>热田神宫</t>
+  </si>
+  <si>
+    <t>爱知县</t>
   </si>
   <si>
     <t>R2-06C34E06EEDF</t>
   </si>
   <si>
-    <t>Yakushima</t>
-  </si>
-  <si>
-    <t>Kagoshima</t>
-  </si>
-  <si>
-    <t>Amanoiwato Shrine</t>
-  </si>
-  <si>
-    <t>Miyazaki</t>
+    <t>屋久岛</t>
+  </si>
+  <si>
+    <t>鹿儿岛县</t>
+  </si>
+  <si>
+    <t>天岩户神社</t>
+  </si>
+  <si>
+    <t>宫崎县</t>
   </si>
   <si>
     <t>R2-F6A06D6F5A25</t>
   </si>
   <si>
-    <t>Sapporo Clock Tower</t>
-  </si>
-  <si>
-    <t>Lake Kawaguchi</t>
-  </si>
-  <si>
-    <t>Yamanashi</t>
+    <t>札幌市钟楼</t>
+  </si>
+  <si>
+    <t>河口湖</t>
+  </si>
+  <si>
+    <t>山梨县</t>
   </si>
   <si>
     <t>R2-2EA091CDA212</t>
   </si>
   <si>
-    <t>Chūson-ji</t>
-  </si>
-  <si>
-    <t>Matsuyama Castle (Iyo)</t>
+    <t>中尊寺</t>
+  </si>
+  <si>
+    <t>松山城</t>
   </si>
   <si>
     <t>R2-B0E7666D66AC</t>
   </si>
   <si>
-    <t>Tōdai-ji</t>
-  </si>
-  <si>
-    <t>Nara</t>
-  </si>
-  <si>
-    <t>Tsurugaoka Hachimangū</t>
-  </si>
-  <si>
-    <t>Kanagawa</t>
+    <t>东大寺</t>
+  </si>
+  <si>
+    <t>奈良县</t>
+  </si>
+  <si>
+    <t>鹤冈八幡宫</t>
+  </si>
+  <si>
+    <t>神奈川县</t>
   </si>
   <si>
     <t>R2-93725199AA57</t>
   </si>
   <si>
-    <t>Kōtoku-in</t>
+    <t>高德院</t>
   </si>
   <si>
     <t>R2-378C5D9B80C0</t>
@@ -483,31 +486,31 @@
     <t>R2-AECA09FB0D5D</t>
   </si>
   <si>
-    <t>Kusatsu Onsen</t>
-  </si>
-  <si>
-    <t>Gunma</t>
-  </si>
-  <si>
-    <t>National Museum of Nature and Science</t>
+    <t>草津温泉</t>
+  </si>
+  <si>
+    <t>群马县</t>
+  </si>
+  <si>
+    <t>国立科学博物馆</t>
   </si>
   <si>
     <t>R2-2DD3FEEE92B6</t>
   </si>
   <si>
-    <t>Ueno Park</t>
-  </si>
-  <si>
-    <t>Meiji Shrine</t>
+    <t>上野公园</t>
+  </si>
+  <si>
+    <t>明治神宫</t>
   </si>
   <si>
     <t>R2-CA32D58277A1</t>
   </si>
   <si>
-    <t>Dōtonbori</t>
-  </si>
-  <si>
-    <t>Food-related place</t>
+    <t>道顿堀</t>
+  </si>
+  <si>
+    <t>美食相关地点</t>
   </si>
   <si>
     <t>R2-955FC38EB16F</t>
@@ -516,43 +519,43 @@
     <t>R2-0712B110903A</t>
   </si>
   <si>
-    <t>Takayama Jin'ya</t>
-  </si>
-  <si>
-    <t>Lake Mashū</t>
+    <t>高山阵屋</t>
+  </si>
+  <si>
+    <t>摩周湖</t>
   </si>
   <si>
     <t>R2-0461395E65D0</t>
   </si>
   <si>
-    <t>Matsushima</t>
-  </si>
-  <si>
-    <t>Hiroshima Peace Memorial Museum</t>
-  </si>
-  <si>
-    <t>Hiroshima</t>
+    <t>松岛</t>
+  </si>
+  <si>
+    <t>广岛和平纪念资料馆</t>
+  </si>
+  <si>
+    <t>广岛县</t>
   </si>
   <si>
     <t>R2-75B89EA20AA2</t>
   </si>
   <si>
-    <t>Nara Park</t>
+    <t>奈良公园</t>
   </si>
   <si>
     <t>R2-048BACE2D26C</t>
   </si>
   <si>
-    <t>Art and educational traveler</t>
-  </si>
-  <si>
-    <t>A traveler prioritizes art, museums, and educational cultural experiences.</t>
-  </si>
-  <si>
-    <t>Matsumoto Castle</t>
-  </si>
-  <si>
-    <t>Arashiyama</t>
+    <t>艺术与文化学习</t>
+  </si>
+  <si>
+    <t>重视艺术、博物馆与具有学习价值的文化体验。</t>
+  </si>
+  <si>
+    <t>松本城</t>
+  </si>
+  <si>
+    <t>岚山</t>
   </si>
   <si>
     <t>R2-4E53A4B3730B</t>
@@ -567,43 +570,43 @@
     <t>R2-04FC9877D67B</t>
   </si>
   <si>
-    <t>Sakurajima</t>
+    <t>樱岛</t>
   </si>
   <si>
     <t>R2-7AD5C9E9BE85</t>
   </si>
   <si>
-    <t>Mount Aso</t>
-  </si>
-  <si>
-    <t>Kumamoto</t>
-  </si>
-  <si>
-    <t>Tottori Sand Dunes</t>
-  </si>
-  <si>
-    <t>Tottori</t>
+    <t>阿苏山</t>
+  </si>
+  <si>
+    <t>熊本县</t>
+  </si>
+  <si>
+    <t>鸟取砂丘</t>
+  </si>
+  <si>
+    <t>鸟取县</t>
   </si>
   <si>
     <t>R2-BFEF5AC6D944</t>
   </si>
   <si>
-    <t>Shibuya Crossing</t>
-  </si>
-  <si>
-    <t>Shopping area</t>
+    <t>涩谷十字路口</t>
+  </si>
+  <si>
+    <t>购物区域</t>
   </si>
   <si>
     <t>R2-400A4947D037</t>
   </si>
   <si>
-    <t>Cape Manzamo</t>
-  </si>
-  <si>
-    <t>Himeji Castle</t>
-  </si>
-  <si>
-    <t>Hyogo</t>
+    <t>万座毛</t>
+  </si>
+  <si>
+    <t>姬路城</t>
+  </si>
+  <si>
+    <t>兵库县</t>
   </si>
   <si>
     <t>R2-3D67A031083F</t>
@@ -615,16 +618,16 @@
     <t>R2-E5942EA2B647</t>
   </si>
   <si>
-    <t>Asahiyama Zoo</t>
+    <t>旭川市旭山动物园</t>
   </si>
   <si>
     <t>R2-E8F4FAD1E450</t>
   </si>
   <si>
-    <t>Yama-dera</t>
-  </si>
-  <si>
-    <t>Yamagata</t>
+    <t>立石寺</t>
+  </si>
+  <si>
+    <t>山形县</t>
   </si>
   <si>
     <t>R2-8AE273B18AFC</t>
@@ -633,7 +636,7 @@
     <t>R2-10588D420A5C</t>
   </si>
   <si>
-    <t>Toyota Commemorative Museum of Industry and Technology</t>
+    <t>丰田产业技术纪念馆</t>
   </si>
   <si>
     <t>R2-00ADD96AD478</t>
@@ -642,7 +645,7 @@
     <t>R2-8552DD8A8527</t>
   </si>
   <si>
-    <t>Shitennō-ji</t>
+    <t>四天王寺</t>
   </si>
   <si>
     <t>R2-0929008B77ED</t>
@@ -654,16 +657,16 @@
     <t>R2-89527A8BFED3</t>
   </si>
   <si>
-    <t>Ginzan Onsen</t>
+    <t>银山温泉</t>
   </si>
   <si>
     <t>R2-80D1E7EB6483</t>
   </si>
   <si>
-    <t>Nikkō Tōshō-gū</t>
-  </si>
-  <si>
-    <t>Tochigi</t>
+    <t>日光东照宫</t>
+  </si>
+  <si>
+    <t>栃木县</t>
   </si>
   <si>
     <t>R2-DDF78AEB63AD</t>
@@ -672,22 +675,22 @@
     <t>R2-6EE2F01629B8</t>
   </si>
   <si>
-    <t>Fuji-Q Highland</t>
-  </si>
-  <si>
-    <t>Sapporo TV Tower</t>
+    <t>富士急高原乐园</t>
+  </si>
+  <si>
+    <t>札幌电视塔</t>
   </si>
   <si>
     <t>R2-A8454258A6FF</t>
   </si>
   <si>
-    <t>Fushimi Inari-taisha</t>
+    <t>伏见稻荷大社</t>
   </si>
   <si>
     <t>R2-A0FC04382E13</t>
   </si>
   <si>
-    <t>Nagasaki Peace Park</t>
+    <t>长崎和平公园</t>
   </si>
   <si>
     <t>R2-5203D1774FF9</t>
@@ -702,16 +705,16 @@
     <t>R2-7FDEA09BF2C3</t>
   </si>
   <si>
-    <t>Gion</t>
+    <t>祇园</t>
   </si>
   <si>
     <t>R2-DC5AC2E3A1A5</t>
   </si>
   <si>
-    <t>Lake Towada</t>
-  </si>
-  <si>
-    <t>Nagoya Castle</t>
+    <t>十和田湖</t>
+  </si>
+  <si>
+    <t>名古屋城</t>
   </si>
   <si>
     <t>R2-C00D37057CDF</t>
@@ -723,7 +726,7 @@
     <t>R2-18E90CE0C753</t>
   </si>
   <si>
-    <t>Naoshima</t>
+    <t>直岛町</t>
   </si>
   <si>
     <t>R2-EA1C539E53F6</t>
@@ -756,13 +759,13 @@
     <t>R2-B455903B240C</t>
   </si>
   <si>
-    <t>Shiretoko National Park</t>
+    <t>知床国立公园</t>
   </si>
   <si>
     <t>R2-32DA2AFA8B28</t>
   </si>
   <si>
-    <t>Yokohama Chinatown</t>
+    <t>横滨中华街</t>
   </si>
   <si>
     <t>R2-331AD7A7C334</t>
@@ -780,13 +783,13 @@
     <t>R2-B9358D5247C6</t>
   </si>
   <si>
-    <t>Kumamoto Castle</t>
+    <t>熊本城</t>
   </si>
   <si>
     <t>R2-60F45272EA0D</t>
   </si>
   <si>
-    <t>Sumiyoshi-taisha</t>
+    <t>住吉大社</t>
   </si>
   <si>
     <t>R2-587DCA044FC9</t>
@@ -804,7 +807,7 @@
     <t>R2-FD48CFB55C6F</t>
   </si>
   <si>
-    <t>Itsukushima Shrine</t>
+    <t>严岛神社</t>
   </si>
   <si>
     <t>R2-55D4C6FDA493</t>
@@ -825,16 +828,16 @@
     <t>R2-42FAC9E48901</t>
   </si>
   <si>
-    <t>Ise Shrine</t>
-  </si>
-  <si>
-    <t>Mie</t>
+    <t>伊势神宫</t>
+  </si>
+  <si>
+    <t>三重县</t>
   </si>
   <si>
     <t>R2-744389E4AD42</t>
   </si>
   <si>
-    <t>Hakone Open-Air Museum</t>
+    <t>箱根雕刻森林美术馆</t>
   </si>
   <si>
     <t>R2-EB590F7D9459</t>
@@ -855,7 +858,7 @@
     <t>R2-7FFA11F079DA</t>
   </si>
   <si>
-    <t>Hiroshima Peace Memorial</t>
+    <t>原子弹爆炸圆顶屋</t>
   </si>
   <si>
     <t>R2-AA3668C3E5E6</t>
@@ -888,10 +891,10 @@
     <t>R2-6D3D4736155B</t>
   </si>
   <si>
-    <t>Tsukiji fish market</t>
-  </si>
-  <si>
-    <t>Market</t>
+    <t>筑地市场</t>
+  </si>
+  <si>
+    <t>市场</t>
   </si>
   <si>
     <t>R2-8A31A9EC9E7D</t>
@@ -918,7 +921,7 @@
     <t>R2-9681E1438223</t>
   </si>
   <si>
-    <t>Okinawa World</t>
+    <t>冲绳世界文化王国·玉泉洞</t>
   </si>
   <si>
     <t>R2-9695A7B48CD6</t>
@@ -972,7 +975,7 @@
     <t>R2-336711D85292</t>
   </si>
   <si>
-    <t>Naruto whirlpools</t>
+    <t>鸣门漩涡</t>
   </si>
   <si>
     <t>R2-07AF2BB96CC4</t>
@@ -987,13 +990,13 @@
     <t>R2-213C7E18ADB8</t>
   </si>
   <si>
-    <t>Kenroku-en</t>
-  </si>
-  <si>
-    <t>Ishikawa</t>
-  </si>
-  <si>
-    <t>Arima Onsen</t>
+    <t>兼六园</t>
+  </si>
+  <si>
+    <t>石川县</t>
+  </si>
+  <si>
+    <t>有马温泉</t>
   </si>
   <si>
     <t>R2-2ECF59D0D5F0</t>
@@ -1002,10 +1005,10 @@
     <t>R2-B61D5CF1F248</t>
   </si>
   <si>
-    <t>Tokyo Disneyland</t>
-  </si>
-  <si>
-    <t>Chiba</t>
+    <t>东京迪士尼乐园</t>
+  </si>
+  <si>
+    <t>千叶县</t>
   </si>
   <si>
     <t>R2-6E82DB3A8587</t>
@@ -1017,103 +1020,109 @@
     <t>R2-3D5C375BDC51</t>
   </si>
   <si>
-    <t>Reviewer Instructions</t>
-  </si>
-  <si>
-    <t>Guidance</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Judge which POI better fits the stated traveler scenario. Judge traveler fit, not your personal favorite.</t>
-  </si>
-  <si>
-    <t>Choose exactly one: A, B, TIE, or INSUFFICIENT_INFO.</t>
-  </si>
-  <si>
-    <t>Choose high, medium, or low for every answered row.</t>
-  </si>
-  <si>
-    <t>Independence</t>
-  </si>
-  <si>
-    <t>Work independently. Do not inspect TASK-038 files, restricted TASK-039 mapping files, scoring code, or another reviewer’s answers.</t>
-  </si>
-  <si>
-    <t>Evidence</t>
-  </si>
-  <si>
-    <t>Source links are neutral identity references. Open them only when identity or broad type is unclear.</t>
-  </si>
-  <si>
-    <t>Out of scope</t>
-  </si>
-  <si>
-    <t>Do not infer live opening hours, queues, weather, route feasibility, booking availability, or price inventory.</t>
-  </si>
-  <si>
-    <t>Insufficient information</t>
-  </si>
-  <si>
-    <t>Use INSUFFICIENT_INFO when the available information cannot support a responsible judgment.</t>
-  </si>
-  <si>
-    <t>Protected cells</t>
-  </si>
-  <si>
-    <t>Do not alter question, identity, or source cells. Only Choice, Confidence, and Note are intended for editing.</t>
-  </si>
-  <si>
-    <t>Privacy</t>
-  </si>
-  <si>
-    <t>Do not enter your name, contact details, or other personal information in Note.</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>reviewVersion</t>
+    <t>评审说明</t>
+  </si>
+  <si>
+    <t>操作指引</t>
+  </si>
+  <si>
+    <t>评审目标</t>
+  </si>
+  <si>
+    <t>判断哪个景点更符合给出的旅行场景。请判断旅客适配度，而不是选择您个人更喜欢的景点。</t>
+  </si>
+  <si>
+    <t>每题只能选择一项：A、B、平局或信息不足。</t>
+  </si>
+  <si>
+    <t>每道已作答题目都必须选择高、中或低。</t>
+  </si>
+  <si>
+    <t>独立性</t>
+  </si>
+  <si>
+    <t>请独立完成评审。不要查看 TASK-038 文件、受限的 TASK-039 映射文件、评分代码或其他评审员的答案。</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>来源链接仅用于中立地确认景点身份。只有当景点身份或大类不明确时才需要打开。</t>
+  </si>
+  <si>
+    <t>评审范围外</t>
+  </si>
+  <si>
+    <t>不要推测实时营业时间、排队情况、天气、路线可行性、预约可用性或价格库存。</t>
+  </si>
+  <si>
+    <t>信息不足</t>
+  </si>
+  <si>
+    <t>当现有信息不足以支持可靠判断时，请选择“信息不足”。</t>
+  </si>
+  <si>
+    <t>受保护单元格</t>
+  </si>
+  <si>
+    <t>请勿修改题目、景点身份或来源单元格。只有“选择”“置信度”和“备注”允许填写。</t>
+  </si>
+  <si>
+    <t>隐私</t>
+  </si>
+  <si>
+    <t>请勿在备注中填写姓名、联系方式或其他个人信息。</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>值</t>
+  </si>
+  <si>
+    <t>评审版本</t>
   </si>
   <si>
     <t>task-039-v1</t>
   </si>
   <si>
-    <t>reviewerCode</t>
+    <t>评审员代码</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>itemCount</t>
-  </si>
-  <si>
-    <t>sourcePackSha256</t>
+    <t>题目数量</t>
+  </si>
+  <si>
+    <t>源题包 SHA-256</t>
   </si>
   <si>
     <t>67782a402cfd999a9a4840d531cb139bf2b5aae6221fde3fd31480b92821fcba</t>
   </si>
   <si>
-    <t>workbookSchemaVersion</t>
-  </si>
-  <si>
-    <t>task-040-xlsx-v1</t>
-  </si>
-  <si>
-    <t>protectedContentDigestAlgorithm</t>
+    <t>工作簿结构版本</t>
+  </si>
+  <si>
+    <t>task-040-xlsx-v2-zh-CN</t>
+  </si>
+  <si>
+    <t>受保护内容摘要算法</t>
   </si>
   <si>
     <t>SHA-256</t>
   </si>
   <si>
-    <t>protectedContentDigest</t>
-  </si>
-  <si>
-    <t>7de05d9c842550fd7f0bb41efc3f0faa4c37e8aefce40cdc104385b1a2b4dc65</t>
+    <t>受保护内容摘要</t>
+  </si>
+  <si>
+    <t>801923a116b56c0d8f2197f228ea0eb3fd7f93693f526a04d31f2e80eb9e9d5f</t>
+  </si>
+  <si>
+    <t>中文本地化目录 SHA-256</t>
+  </si>
+  <si>
+    <t>3598c6559a2ab5641091be1954c3e86b2ee62fb94b42c6a8a860de3b5e4a3b12</t>
   </si>
 </sst>
 </file>
@@ -1745,10 +1754,10 @@
         <v>36</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>26</v>
@@ -1757,16 +1766,16 @@
         <v>27</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>30</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>26</v>
@@ -1783,25 +1792,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>26</v>
@@ -1810,7 +1819,7 @@
         <v>27</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
@@ -1819,7 +1828,7 @@
         <v>30</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>26</v>
@@ -1836,25 +1845,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>26</v>
@@ -1863,16 +1872,16 @@
         <v>27</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>26</v>
@@ -1889,16 +1898,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>29</v>
@@ -1907,7 +1916,7 @@
         <v>30</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>26</v>
@@ -1916,16 +1925,16 @@
         <v>27</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>26</v>
@@ -1942,25 +1951,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>26</v>
@@ -1969,16 +1978,16 @@
         <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O7" s="11" t="s">
         <v>26</v>
@@ -1995,26 +2004,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="I8" s="6" t="s">
         <v>26</v>
       </c>
@@ -2022,16 +2031,16 @@
         <v>27</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>26</v>
@@ -2048,43 +2057,43 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="I9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="M9" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="N9" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>26</v>
@@ -2101,13 +2110,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>28</v>
@@ -2128,16 +2137,16 @@
         <v>27</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>26</v>
@@ -2154,22 +2163,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>25</v>
@@ -2181,13 +2190,13 @@
         <v>27</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>31</v>
@@ -2207,7 +2216,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
@@ -2216,16 +2225,16 @@
         <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>26</v>
@@ -2234,16 +2243,16 @@
         <v>27</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>26</v>
@@ -2260,7 +2269,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>20</v>
@@ -2269,16 +2278,16 @@
         <v>21</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>26</v>
@@ -2287,13 +2296,13 @@
         <v>27</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N13" s="10" t="s">
         <v>31</v>
@@ -2313,25 +2322,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>26</v>
@@ -2340,7 +2349,7 @@
         <v>27</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>23</v>
@@ -2349,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>26</v>
@@ -2366,7 +2375,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>33</v>
@@ -2375,16 +2384,16 @@
         <v>34</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>26</v>
@@ -2393,16 +2402,16 @@
         <v>27</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>26</v>
@@ -2419,16 +2428,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>23</v>
@@ -2437,7 +2446,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>26</v>
@@ -2446,16 +2455,16 @@
         <v>27</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>26</v>
@@ -2472,25 +2481,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>26</v>
@@ -2499,16 +2508,16 @@
         <v>27</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O17" s="11" t="s">
         <v>26</v>
@@ -2525,25 +2534,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>26</v>
@@ -2552,16 +2561,16 @@
         <v>27</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>26</v>
@@ -2578,25 +2587,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>26</v>
@@ -2605,16 +2614,16 @@
         <v>27</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" s="11" t="s">
         <v>26</v>
@@ -2631,25 +2640,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>26</v>
@@ -2658,16 +2667,16 @@
         <v>27</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>26</v>
@@ -2684,25 +2693,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>26</v>
@@ -2711,16 +2720,16 @@
         <v>27</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O21" s="11" t="s">
         <v>26</v>
@@ -2737,25 +2746,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>26</v>
@@ -2764,16 +2773,16 @@
         <v>27</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>26</v>
@@ -2790,25 +2799,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>26</v>
@@ -2817,16 +2826,16 @@
         <v>27</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O23" s="11" t="s">
         <v>26</v>
@@ -2843,25 +2852,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>26</v>
@@ -2870,16 +2879,16 @@
         <v>27</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>26</v>
@@ -2896,25 +2905,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>26</v>
@@ -2923,16 +2932,16 @@
         <v>27</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O25" s="11" t="s">
         <v>26</v>
@@ -2949,25 +2958,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="G26" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>26</v>
@@ -2976,16 +2985,16 @@
         <v>27</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>26</v>
@@ -3002,25 +3011,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>26</v>
@@ -3029,16 +3038,16 @@
         <v>27</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="11" t="s">
         <v>26</v>
@@ -3055,43 +3064,43 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L28" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>75</v>
-      </c>
       <c r="M28" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>26</v>
@@ -3108,43 +3117,43 @@
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="L29" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="M29" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O29" s="11" t="s">
         <v>26</v>
@@ -3161,25 +3170,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>26</v>
@@ -3188,16 +3197,16 @@
         <v>27</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>26</v>
@@ -3214,25 +3223,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>26</v>
@@ -3241,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>29</v>
@@ -3250,7 +3259,7 @@
         <v>30</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O31" s="11" t="s">
         <v>26</v>
@@ -3267,25 +3276,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>26</v>
@@ -3294,16 +3303,16 @@
         <v>27</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>26</v>
@@ -3320,7 +3329,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>20</v>
@@ -3329,16 +3338,16 @@
         <v>21</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>26</v>
@@ -3347,16 +3356,16 @@
         <v>27</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O33" s="11" t="s">
         <v>26</v>
@@ -3373,19 +3382,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>30</v>
@@ -3400,16 +3409,16 @@
         <v>27</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>26</v>
@@ -3426,25 +3435,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>26</v>
@@ -3453,7 +3462,7 @@
         <v>27</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>29</v>
@@ -3462,7 +3471,7 @@
         <v>30</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O35" s="11" t="s">
         <v>26</v>
@@ -3479,25 +3488,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>26</v>
@@ -3506,16 +3515,16 @@
         <v>27</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>26</v>
@@ -3532,13 +3541,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>22</v>
@@ -3559,16 +3568,16 @@
         <v>27</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O37" s="11" t="s">
         <v>26</v>
@@ -3585,16 +3594,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>29</v>
@@ -3603,7 +3612,7 @@
         <v>30</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>26</v>
@@ -3612,16 +3621,16 @@
         <v>27</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>26</v>
@@ -3638,25 +3647,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>26</v>
@@ -3665,16 +3674,16 @@
         <v>27</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O39" s="11" t="s">
         <v>26</v>
@@ -3691,25 +3700,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>26</v>
@@ -3718,16 +3727,16 @@
         <v>27</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>26</v>
@@ -3744,25 +3753,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>26</v>
@@ -3771,16 +3780,16 @@
         <v>27</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O41" s="11" t="s">
         <v>26</v>
@@ -3797,7 +3806,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
@@ -3806,16 +3815,16 @@
         <v>21</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>26</v>
@@ -3824,16 +3833,16 @@
         <v>27</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>26</v>
@@ -3850,16 +3859,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>23</v>
@@ -3868,7 +3877,7 @@
         <v>24</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I43" s="11" t="s">
         <v>26</v>
@@ -3877,16 +3886,16 @@
         <v>27</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O43" s="11" t="s">
         <v>26</v>
@@ -3903,43 +3912,43 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H44" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="N44" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>26</v>
@@ -3956,25 +3965,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>26</v>
@@ -3983,16 +3992,16 @@
         <v>27</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O45" s="11" t="s">
         <v>26</v>
@@ -4009,25 +4018,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>26</v>
@@ -4036,16 +4045,16 @@
         <v>27</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>26</v>
@@ -4062,25 +4071,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>26</v>
@@ -4089,16 +4098,16 @@
         <v>27</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O47" s="11" t="s">
         <v>26</v>
@@ -4115,25 +4124,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>26</v>
@@ -4142,16 +4151,16 @@
         <v>27</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>26</v>
@@ -4168,43 +4177,43 @@
         <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="I49" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="M49" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O49" s="11" t="s">
         <v>26</v>
@@ -4221,25 +4230,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>26</v>
@@ -4248,16 +4257,16 @@
         <v>27</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>26</v>
@@ -4274,25 +4283,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I51" s="11" t="s">
         <v>26</v>
@@ -4301,16 +4310,16 @@
         <v>27</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O51" s="11" t="s">
         <v>26</v>
@@ -4327,25 +4336,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>26</v>
@@ -4354,16 +4363,16 @@
         <v>27</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>26</v>
@@ -4380,13 +4389,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>28</v>
@@ -4407,16 +4416,16 @@
         <v>27</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L53" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M53" s="10" t="s">
         <v>24</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O53" s="11" t="s">
         <v>26</v>
@@ -4433,13 +4442,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>22</v>
@@ -4460,16 +4469,16 @@
         <v>27</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L54" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N54" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>26</v>
@@ -4486,25 +4495,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I55" s="11" t="s">
         <v>26</v>
@@ -4513,7 +4522,7 @@
         <v>27</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L55" s="10" t="s">
         <v>23</v>
@@ -4522,7 +4531,7 @@
         <v>24</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O55" s="11" t="s">
         <v>26</v>
@@ -4539,25 +4548,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>26</v>
@@ -4566,16 +4575,16 @@
         <v>27</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L56" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>26</v>
@@ -4592,25 +4601,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" s="11" t="s">
         <v>26</v>
@@ -4619,7 +4628,7 @@
         <v>27</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L57" s="10" t="s">
         <v>29</v>
@@ -4628,7 +4637,7 @@
         <v>30</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O57" s="11" t="s">
         <v>26</v>
@@ -4645,22 +4654,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>25</v>
@@ -4672,16 +4681,16 @@
         <v>27</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L58" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N58" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>26</v>
@@ -4698,22 +4707,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>25</v>
@@ -4725,16 +4734,16 @@
         <v>27</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L59" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O59" s="11" t="s">
         <v>26</v>
@@ -4751,25 +4760,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>26</v>
@@ -4778,16 +4787,16 @@
         <v>27</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
@@ -4804,13 +4813,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>28</v>
@@ -4831,7 +4840,7 @@
         <v>27</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L61" s="10" t="s">
         <v>23</v>
@@ -4840,7 +4849,7 @@
         <v>24</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O61" s="11" t="s">
         <v>26</v>
@@ -4857,16 +4866,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>29</v>
@@ -4875,7 +4884,7 @@
         <v>30</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>26</v>
@@ -4884,16 +4893,16 @@
         <v>27</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N62" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>26</v>
@@ -4910,16 +4919,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>23</v>
@@ -4928,25 +4937,25 @@
         <v>24</v>
       </c>
       <c r="H63" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="M63" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I63" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K63" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="L63" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="M63" s="10" t="s">
-        <v>46</v>
-      </c>
       <c r="N63" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O63" s="11" t="s">
         <v>26</v>
@@ -4963,25 +4972,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>26</v>
@@ -4990,16 +4999,16 @@
         <v>27</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N64" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>26</v>
@@ -5016,25 +5025,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I65" s="11" t="s">
         <v>26</v>
@@ -5043,16 +5052,16 @@
         <v>27</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L65" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O65" s="11" t="s">
         <v>26</v>
@@ -5069,25 +5078,25 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>26</v>
@@ -5096,16 +5105,16 @@
         <v>27</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>26</v>
@@ -5122,25 +5131,25 @@
         <v>66</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I67" s="11" t="s">
         <v>26</v>
@@ -5149,16 +5158,16 @@
         <v>27</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L67" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M67" s="10" t="s">
         <v>24</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O67" s="11" t="s">
         <v>26</v>
@@ -5175,7 +5184,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>33</v>
@@ -5184,16 +5193,16 @@
         <v>34</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>26</v>
@@ -5202,16 +5211,16 @@
         <v>27</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L68" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N68" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>26</v>
@@ -5228,40 +5237,40 @@
         <v>68</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F69" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K69" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I69" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K69" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="L69" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N69" s="10" t="s">
         <v>25</v>
@@ -5281,25 +5290,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>26</v>
@@ -5308,16 +5317,16 @@
         <v>27</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L70" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N70" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>26</v>
@@ -5334,25 +5343,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I71" s="11" t="s">
         <v>26</v>
@@ -5361,7 +5370,7 @@
         <v>27</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L71" s="10" t="s">
         <v>29</v>
@@ -5370,7 +5379,7 @@
         <v>30</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O71" s="11" t="s">
         <v>26</v>
@@ -5387,25 +5396,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>26</v>
@@ -5414,16 +5423,16 @@
         <v>27</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L72" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N72" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>26</v>
@@ -5440,25 +5449,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I73" s="11" t="s">
         <v>26</v>
@@ -5467,16 +5476,16 @@
         <v>27</v>
       </c>
       <c r="K73" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L73" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O73" s="11" t="s">
         <v>26</v>
@@ -5493,7 +5502,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>33</v>
@@ -5502,16 +5511,16 @@
         <v>34</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>26</v>
@@ -5520,7 +5529,7 @@
         <v>27</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>29</v>
@@ -5529,7 +5538,7 @@
         <v>30</v>
       </c>
       <c r="N74" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>26</v>
@@ -5546,25 +5555,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I75" s="11" t="s">
         <v>26</v>
@@ -5573,16 +5582,16 @@
         <v>27</v>
       </c>
       <c r="K75" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L75" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O75" s="11" t="s">
         <v>26</v>
@@ -5599,25 +5608,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>26</v>
@@ -5626,16 +5635,16 @@
         <v>27</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L76" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N76" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>26</v>
@@ -5652,25 +5661,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I77" s="11" t="s">
         <v>26</v>
@@ -5679,16 +5688,16 @@
         <v>27</v>
       </c>
       <c r="K77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O77" s="11" t="s">
         <v>26</v>
@@ -5705,7 +5714,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>33</v>
@@ -5714,16 +5723,16 @@
         <v>34</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>26</v>
@@ -5732,16 +5741,16 @@
         <v>27</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>26</v>
@@ -5758,25 +5767,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I79" s="11" t="s">
         <v>26</v>
@@ -5785,16 +5794,16 @@
         <v>27</v>
       </c>
       <c r="K79" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L79" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O79" s="11" t="s">
         <v>26</v>
@@ -5811,25 +5820,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>26</v>
@@ -5838,16 +5847,16 @@
         <v>27</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>26</v>
@@ -5864,43 +5873,43 @@
         <v>80</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H81" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K81" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="L81" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M81" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I81" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K81" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L81" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="N81" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O81" s="11" t="s">
         <v>26</v>
@@ -5917,25 +5926,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>26</v>
@@ -5944,16 +5953,16 @@
         <v>27</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>26</v>
@@ -5970,25 +5979,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I83" s="11" t="s">
         <v>26</v>
@@ -5997,16 +6006,16 @@
         <v>27</v>
       </c>
       <c r="K83" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L83" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M83" s="10" t="s">
         <v>30</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O83" s="11" t="s">
         <v>26</v>
@@ -6023,25 +6032,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>26</v>
@@ -6050,16 +6059,16 @@
         <v>27</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L84" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M84" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>26</v>
@@ -6076,16 +6085,16 @@
         <v>84</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>29</v>
@@ -6094,22 +6103,22 @@
         <v>30</v>
       </c>
       <c r="H85" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M85" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="I85" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K85" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="N85" s="10" t="s">
         <v>31</v>
@@ -6129,25 +6138,25 @@
         <v>85</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>26</v>
@@ -6156,16 +6165,16 @@
         <v>27</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M86" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
@@ -6182,43 +6191,43 @@
         <v>86</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E87" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I87" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="L87" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I87" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K87" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="M87" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O87" s="11" t="s">
         <v>26</v>
@@ -6235,25 +6244,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>26</v>
@@ -6262,16 +6271,16 @@
         <v>27</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L88" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>26</v>
@@ -6288,25 +6297,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I89" s="11" t="s">
         <v>26</v>
@@ -6315,13 +6324,13 @@
         <v>27</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L89" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N89" s="10" t="s">
         <v>31</v>
@@ -6341,25 +6350,25 @@
         <v>89</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I90" s="6" t="s">
         <v>26</v>
@@ -6368,7 +6377,7 @@
         <v>27</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>23</v>
@@ -6377,7 +6386,7 @@
         <v>24</v>
       </c>
       <c r="N90" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>26</v>
@@ -6394,43 +6403,43 @@
         <v>90</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F91" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K91" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="G91" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I91" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K91" s="10" t="s">
-        <v>186</v>
-      </c>
       <c r="L91" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O91" s="11" t="s">
         <v>26</v>
@@ -6447,7 +6456,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>33</v>
@@ -6456,34 +6465,34 @@
         <v>34</v>
       </c>
       <c r="E92" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M92" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F92" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L92" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M92" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="N92" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>26</v>
@@ -6500,25 +6509,25 @@
         <v>92</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I93" s="11" t="s">
         <v>26</v>
@@ -6527,13 +6536,13 @@
         <v>27</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L93" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N93" s="10" t="s">
         <v>25</v>
@@ -6553,25 +6562,25 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>26</v>
@@ -6580,16 +6589,16 @@
         <v>27</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N94" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>26</v>
@@ -6606,7 +6615,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>20</v>
@@ -6615,16 +6624,16 @@
         <v>21</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I95" s="11" t="s">
         <v>26</v>
@@ -6633,16 +6642,16 @@
         <v>27</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L95" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O95" s="11" t="s">
         <v>26</v>
@@ -6659,25 +6668,25 @@
         <v>95</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I96" s="6" t="s">
         <v>26</v>
@@ -6686,16 +6695,16 @@
         <v>27</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N96" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>26</v>
@@ -6712,25 +6721,25 @@
         <v>96</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I97" s="11" t="s">
         <v>26</v>
@@ -6739,16 +6748,16 @@
         <v>27</v>
       </c>
       <c r="K97" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L97" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O97" s="11" t="s">
         <v>26</v>
@@ -6765,16 +6774,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>23</v>
@@ -6783,7 +6792,7 @@
         <v>24</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I98" s="6" t="s">
         <v>26</v>
@@ -6792,16 +6801,16 @@
         <v>27</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L98" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M98" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>26</v>
@@ -6818,25 +6827,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" s="11" t="s">
         <v>26</v>
@@ -6845,13 +6854,13 @@
         <v>27</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L99" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N99" s="10" t="s">
         <v>25</v>
@@ -6871,7 +6880,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>20</v>
@@ -6880,16 +6889,16 @@
         <v>21</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>26</v>
@@ -6898,16 +6907,16 @@
         <v>27</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L100" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>26</v>
@@ -6924,25 +6933,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I101" s="11" t="s">
         <v>26</v>
@@ -6951,16 +6960,16 @@
         <v>27</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L101" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O101" s="11" t="s">
         <v>26</v>
@@ -6977,25 +6986,25 @@
         <v>101</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>26</v>
@@ -7004,7 +7013,7 @@
         <v>27</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>29</v>
@@ -7013,7 +7022,7 @@
         <v>30</v>
       </c>
       <c r="N102" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>26</v>
@@ -7030,25 +7039,25 @@
         <v>102</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G103" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I103" s="11" t="s">
         <v>26</v>
@@ -7057,16 +7066,16 @@
         <v>27</v>
       </c>
       <c r="K103" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L103" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O103" s="11" t="s">
         <v>26</v>
@@ -7083,25 +7092,25 @@
         <v>103</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I104" s="6" t="s">
         <v>26</v>
@@ -7110,16 +7119,16 @@
         <v>27</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>26</v>
@@ -7136,7 +7145,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>33</v>
@@ -7145,16 +7154,16 @@
         <v>34</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I105" s="11" t="s">
         <v>26</v>
@@ -7163,16 +7172,16 @@
         <v>27</v>
       </c>
       <c r="K105" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L105" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M105" s="10" t="s">
         <v>24</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O105" s="11" t="s">
         <v>26</v>
@@ -7189,25 +7198,25 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I106" s="6" t="s">
         <v>26</v>
@@ -7216,16 +7225,16 @@
         <v>27</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>26</v>
@@ -7242,7 +7251,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>20</v>
@@ -7251,16 +7260,16 @@
         <v>21</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G107" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I107" s="11" t="s">
         <v>26</v>
@@ -7269,16 +7278,16 @@
         <v>27</v>
       </c>
       <c r="K107" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M107" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N107" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="L107" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M107" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N107" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="O107" s="11" t="s">
         <v>26</v>
@@ -7295,22 +7304,22 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>31</v>
@@ -7322,16 +7331,16 @@
         <v>27</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
@@ -7348,43 +7357,43 @@
         <v>108</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J109" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K109" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L109" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H109" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I109" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J109" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K109" s="10" t="s">
+      <c r="M109" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N109" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="L109" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M109" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N109" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="O109" s="11" t="s">
         <v>26</v>
@@ -7401,25 +7410,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>26</v>
@@ -7428,16 +7437,16 @@
         <v>27</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>26</v>
@@ -7454,7 +7463,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>20</v>
@@ -7463,34 +7472,34 @@
         <v>21</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="I111" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J111" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="L111" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H111" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I111" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J111" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K111" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="L111" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="M111" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O111" s="11" t="s">
         <v>26</v>
@@ -7507,25 +7516,25 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I112" s="6" t="s">
         <v>26</v>
@@ -7534,16 +7543,16 @@
         <v>27</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L112" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>26</v>
@@ -7560,25 +7569,25 @@
         <v>112</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G113" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I113" s="11" t="s">
         <v>26</v>
@@ -7587,16 +7596,16 @@
         <v>27</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L113" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O113" s="11" t="s">
         <v>26</v>
@@ -7613,25 +7622,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I114" s="6" t="s">
         <v>26</v>
@@ -7640,16 +7649,16 @@
         <v>27</v>
       </c>
       <c r="K114" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L114" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>26</v>
@@ -7666,25 +7675,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I115" s="11" t="s">
         <v>26</v>
@@ -7693,16 +7702,16 @@
         <v>27</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L115" s="10" t="s">
         <v>36</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O115" s="11" t="s">
         <v>26</v>
@@ -7719,7 +7728,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>20</v>
@@ -7728,16 +7737,16 @@
         <v>21</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I116" s="6" t="s">
         <v>26</v>
@@ -7772,16 +7781,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>23</v>
@@ -7790,7 +7799,7 @@
         <v>24</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I117" s="11" t="s">
         <v>26</v>
@@ -7799,16 +7808,16 @@
         <v>27</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L117" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O117" s="11" t="s">
         <v>26</v>
@@ -7825,7 +7834,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>20</v>
@@ -7834,16 +7843,16 @@
         <v>21</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I118" s="6" t="s">
         <v>26</v>
@@ -7852,16 +7861,16 @@
         <v>27</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M118" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N118" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>26</v>
@@ -7878,25 +7887,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I119" s="11" t="s">
         <v>26</v>
@@ -7905,16 +7914,16 @@
         <v>27</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L119" s="10" t="s">
         <v>36</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O119" s="11" t="s">
         <v>26</v>
@@ -7931,43 +7940,43 @@
         <v>119</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E120" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K120" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F120" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J120" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K120" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="L120" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M120" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N120" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>26</v>
@@ -7984,25 +7993,25 @@
         <v>120</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G121" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I121" s="11" t="s">
         <v>26</v>
@@ -8011,16 +8020,16 @@
         <v>27</v>
       </c>
       <c r="K121" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L121" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O121" s="11" t="s">
         <v>26</v>
@@ -8037,7 +8046,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>20</v>
@@ -8046,16 +8055,16 @@
         <v>21</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I122" s="6" t="s">
         <v>26</v>
@@ -8064,16 +8073,16 @@
         <v>27</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L122" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N122" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>26</v>
@@ -8090,16 +8099,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>23</v>
@@ -8108,7 +8117,7 @@
         <v>24</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I123" s="11" t="s">
         <v>26</v>
@@ -8117,16 +8126,16 @@
         <v>27</v>
       </c>
       <c r="K123" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L123" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M123" s="10" t="s">
         <v>24</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O123" s="11" t="s">
         <v>26</v>
@@ -8143,25 +8152,25 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I124" s="6" t="s">
         <v>26</v>
@@ -8170,16 +8179,16 @@
         <v>27</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N124" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>26</v>
@@ -8196,25 +8205,25 @@
         <v>124</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G125" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I125" s="11" t="s">
         <v>26</v>
@@ -8223,16 +8232,16 @@
         <v>27</v>
       </c>
       <c r="K125" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L125" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M125" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O125" s="11" t="s">
         <v>26</v>
@@ -8249,7 +8258,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>33</v>
@@ -8276,13 +8285,13 @@
         <v>27</v>
       </c>
       <c r="K126" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L126" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N126" s="5" t="s">
         <v>31</v>
@@ -8302,25 +8311,25 @@
         <v>126</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I127" s="11" t="s">
         <v>26</v>
@@ -8329,7 +8338,7 @@
         <v>27</v>
       </c>
       <c r="K127" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L127" s="10" t="s">
         <v>23</v>
@@ -8338,7 +8347,7 @@
         <v>24</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O127" s="11" t="s">
         <v>26</v>
@@ -8355,16 +8364,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>23</v>
@@ -8373,7 +8382,7 @@
         <v>24</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I128" s="6" t="s">
         <v>26</v>
@@ -8382,16 +8391,16 @@
         <v>27</v>
       </c>
       <c r="K128" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L128" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N128" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>26</v>
@@ -8408,7 +8417,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>33</v>
@@ -8417,16 +8426,16 @@
         <v>34</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I129" s="11" t="s">
         <v>26</v>
@@ -8435,16 +8444,16 @@
         <v>27</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L129" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M129" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O129" s="11" t="s">
         <v>26</v>
@@ -8461,25 +8470,25 @@
         <v>129</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I130" s="6" t="s">
         <v>26</v>
@@ -8488,16 +8497,16 @@
         <v>27</v>
       </c>
       <c r="K130" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L130" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N130" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>26</v>
@@ -8514,16 +8523,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>29</v>
@@ -8532,7 +8541,7 @@
         <v>30</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I131" s="11" t="s">
         <v>26</v>
@@ -8541,16 +8550,16 @@
         <v>27</v>
       </c>
       <c r="K131" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L131" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M131" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O131" s="11" t="s">
         <v>26</v>
@@ -8567,7 +8576,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>33</v>
@@ -8576,16 +8585,16 @@
         <v>34</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I132" s="6" t="s">
         <v>26</v>
@@ -8594,16 +8603,16 @@
         <v>27</v>
       </c>
       <c r="K132" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L132" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M132" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N132" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>26</v>
@@ -8620,25 +8629,25 @@
         <v>132</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I133" s="11" t="s">
         <v>26</v>
@@ -8647,13 +8656,13 @@
         <v>27</v>
       </c>
       <c r="K133" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L133" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M133" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N133" s="10" t="s">
         <v>25</v>
@@ -8673,25 +8682,25 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I134" s="6" t="s">
         <v>26</v>
@@ -8700,16 +8709,16 @@
         <v>27</v>
       </c>
       <c r="K134" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M134" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N134" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>26</v>
@@ -8726,25 +8735,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I135" s="11" t="s">
         <v>26</v>
@@ -8753,16 +8762,16 @@
         <v>27</v>
       </c>
       <c r="K135" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L135" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O135" s="11" t="s">
         <v>26</v>
@@ -8779,25 +8788,25 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I136" s="6" t="s">
         <v>26</v>
@@ -8806,16 +8815,16 @@
         <v>27</v>
       </c>
       <c r="K136" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L136" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M136" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N136" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>26</v>
@@ -8832,25 +8841,25 @@
         <v>136</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I137" s="11" t="s">
         <v>26</v>
@@ -8859,16 +8868,16 @@
         <v>27</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L137" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O137" s="11" t="s">
         <v>26</v>
@@ -8885,43 +8894,43 @@
         <v>137</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H138" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J138" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K138" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L138" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M138" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J138" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K138" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="L138" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="M138" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="N138" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>26</v>
@@ -8938,25 +8947,25 @@
         <v>138</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I139" s="11" t="s">
         <v>26</v>
@@ -8965,16 +8974,16 @@
         <v>27</v>
       </c>
       <c r="K139" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L139" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M139" s="10" t="s">
         <v>30</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O139" s="11" t="s">
         <v>26</v>
@@ -8991,7 +9000,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>33</v>
@@ -9000,13 +9009,13 @@
         <v>34</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>31</v>
@@ -9018,16 +9027,16 @@
         <v>27</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L140" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M140" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N140" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>26</v>
@@ -9044,16 +9053,16 @@
         <v>140</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>29</v>
@@ -9062,7 +9071,7 @@
         <v>30</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I141" s="11" t="s">
         <v>26</v>
@@ -9071,16 +9080,16 @@
         <v>27</v>
       </c>
       <c r="K141" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L141" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M141" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O141" s="11" t="s">
         <v>26</v>
@@ -9097,25 +9106,25 @@
         <v>141</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I142" s="6" t="s">
         <v>26</v>
@@ -9124,16 +9133,16 @@
         <v>27</v>
       </c>
       <c r="K142" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L142" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N142" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>26</v>
@@ -9150,25 +9159,25 @@
         <v>142</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I143" s="11" t="s">
         <v>26</v>
@@ -9177,16 +9186,16 @@
         <v>27</v>
       </c>
       <c r="K143" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L143" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M143" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O143" s="11" t="s">
         <v>26</v>
@@ -9203,16 +9212,16 @@
         <v>143</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>23</v>
@@ -9221,7 +9230,7 @@
         <v>24</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I144" s="6" t="s">
         <v>26</v>
@@ -9230,13 +9239,13 @@
         <v>27</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L144" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N144" s="5" t="s">
         <v>31</v>
@@ -9256,7 +9265,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>33</v>
@@ -9265,16 +9274,16 @@
         <v>34</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G145" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I145" s="11" t="s">
         <v>26</v>
@@ -9283,13 +9292,13 @@
         <v>27</v>
       </c>
       <c r="K145" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L145" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M145" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N145" s="10" t="s">
         <v>31</v>
@@ -9308,17 +9317,17 @@
   <sheetProtection sheet="1" selectLockedCells="1" autoFilter="0"/>
   <autoFilter ref="A1:S145"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose A, B, TIE, or INSUFFICIENT_INFO." sqref="Q10:Q145">
-      <formula1>"A,B,TIE,INSUFFICIENT_INFO"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="选择无效" error="请选择 A、B、平局或信息不足。" sqref="Q10:Q145">
+      <formula1>"A,B,平局,信息不足"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid choice" error="Choose A, B, TIE, or INSUFFICIENT_INFO." sqref="Q2:Q145">
-      <formula1>"A,B,TIE,INSUFFICIENT_INFO"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="选择无效" error="请选择 A、B、平局或信息不足。" sqref="Q2:Q145">
+      <formula1>"A,B,平局,信息不足"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid confidence" error="Choose high, medium, or low." sqref="R10:R145">
-      <formula1>"high,medium,low"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="置信度无效" error="请选择高、中或低。" sqref="R10:R145">
+      <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid confidence" error="Choose high, medium, or low." sqref="R2:R145">
-      <formula1>"high,medium,low"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="置信度无效" error="请选择高、中或低。" sqref="R2:R145">
+      <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -9915,18 +9924,18 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9934,7 +9943,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9942,55 +9951,55 @@
         <v>17</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -10002,7 +10011,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10011,31 +10020,31 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B4" s="15">
         <v>144</v>
@@ -10043,34 +10052,42 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
